--- a/configs/schemas/main.xlsx
+++ b/configs/schemas/main.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/madeliri/Desktop/project_common/configs/schemas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/madeliri/Documents/git/shiny_form/configs/schemas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF96B9BC-DE4F-D74D-B99F-66ADB3322044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07037598-774F-A843-9C67-26D8CBECEED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="20340" xr2:uid="{9A1397C5-2914-6B46-9457-B60C998D9C07}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="30240" windowHeight="19000" xr2:uid="{9A1397C5-2914-6B46-9457-B60C998D9C07}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="76">
   <si>
     <t>part</t>
   </si>
@@ -233,18 +233,12 @@
     <t>example_description2</t>
   </si>
   <si>
-    <t>&lt;hr&gt;&lt;b style="color:black; font-size: large;"&gt;Пример стилизованного текста&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>required</t>
   </si>
   <si>
     <t>example_validation</t>
   </si>
   <si>
-    <t>Число, обязательное к запонению (но значение должно быть между 0 и 250)</t>
-  </si>
-  <si>
     <t>example_validation_descr</t>
   </si>
   <si>
@@ -252,13 +246,31 @@
   </si>
   <si>
     <t>Демонстрация проверки заполнения полей, и значений.</t>
+  </si>
+  <si>
+    <t>form_description</t>
+  </si>
+  <si>
+    <t>aboba</t>
+  </si>
+  <si>
+    <t>description_header</t>
+  </si>
+  <si>
+    <t>Пример заголовка</t>
+  </si>
+  <si>
+    <t>Число, обязательное к запонению</t>
+  </si>
+  <si>
+    <t>но значение должно быть между 0 и 250</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -290,6 +302,13 @@
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -334,7 +353,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -347,6 +366,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -694,19 +714,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DDED1F0-0BDB-364F-8AF4-EDF00BBB7CEB}">
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" style="7" customWidth="1"/>
     <col min="2" max="2" width="33" style="7" customWidth="1"/>
-    <col min="3" max="3" width="28.33203125" customWidth="1"/>
-    <col min="4" max="4" width="52.1640625" style="7" customWidth="1"/>
-    <col min="5" max="5" width="15.5" customWidth="1"/>
-    <col min="6" max="6" width="23.83203125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="23.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" customWidth="1"/>
+    <col min="5" max="5" width="42.5" style="7" customWidth="1"/>
+    <col min="6" max="6" width="31.6640625" customWidth="1"/>
+    <col min="7" max="7" width="23.83203125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="23.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -716,23 +737,26 @@
       <c r="C1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I1" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>20</v>
       </c>
@@ -742,347 +766,378 @@
       <c r="C2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="6"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F2" s="12"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="6"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="6"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F3" s="12"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C4" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="6"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F4" s="12"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="6"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="12"/>
+      <c r="G5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="6"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="6"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="5" t="s">
+      <c r="D6" s="6"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="6"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="6"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C7" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="12"/>
+      <c r="G7" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G7" s="6"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="6"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="5" t="s">
+      <c r="D8" s="6"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="6"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="6"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C9" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="12"/>
+      <c r="G9" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G9" s="6"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="6"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="5" t="s">
+      <c r="D10" s="6"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G10" s="6"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="6"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C11" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="12"/>
+      <c r="G11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G11" s="6"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H11" s="6"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="5" t="s">
+      <c r="D12" s="6"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G12" s="6"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H12" s="6"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C13" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="6"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F13" s="12"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="6"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C14" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F14" s="5"/>
-      <c r="G14" s="6"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D14" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F14" s="12"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="6"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B15" s="7" t="s">
         <v>36</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="12"/>
+      <c r="G15" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G15" s="6"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H15" s="6"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B16" s="7" t="s">
         <v>44</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="5" t="s">
+      <c r="D17" s="6"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="G17" s="6"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H17" s="6"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C18" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F18" s="5"/>
-      <c r="G18" s="6" t="s">
+      <c r="F18" s="12"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="6" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C19" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E19" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="12"/>
+      <c r="G19" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="5" t="s">
+      <c r="D20" s="6"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="G20" s="6"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H20" s="6"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C21" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F21" s="5"/>
-      <c r="G21" s="6" t="s">
+      <c r="F21" s="12"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C22" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E22" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="12"/>
+      <c r="G22" s="5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="5" t="s">
+      <c r="D23" s="6"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="5" t="s">
+      <c r="D24" s="6"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G24" s="6"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H24" s="6"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C25" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E25" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F25" s="5"/>
-      <c r="G25" s="6" t="s">
+      <c r="F25" s="12"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B26" s="7" t="s">
         <v>62</v>
       </c>
       <c r="C26" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D26" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G26" s="6"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F26" s="12"/>
+      <c r="H26" s="6"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C27" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E27" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G27" s="6"/>
-      <c r="H27">
+      <c r="E27" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F27" s="12"/>
+      <c r="H27" s="6"/>
+      <c r="I27">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C28" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D28" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="D28" t="s">
         <v>8</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="E28" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="G28" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="G28" s="6"/>
-      <c r="H28">
+      <c r="H28" s="6"/>
+      <c r="I28">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
         <v>17</v>
       </c>
@@ -1092,20 +1147,51 @@
       <c r="C29" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" s="2"/>
-      <c r="G29" s="1"/>
-      <c r="H29">
+      <c r="F29" s="12"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="1"/>
+      <c r="I29">
         <v>1</v>
       </c>
     </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F30" s="12"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F31" s="12"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F32" s="12"/>
+    </row>
+    <row r="33" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F33" s="12"/>
+    </row>
+    <row r="34" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F34" s="12"/>
+    </row>
+    <row r="35" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F35" s="12"/>
+    </row>
+    <row r="36" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F36" s="12"/>
+    </row>
+    <row r="37" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F37" s="12"/>
+    </row>
+    <row r="38" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F38" s="6"/>
+    </row>
+    <row r="39" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F39" s="6"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C1:C1048576">
+  <conditionalFormatting sqref="C30:D1048576 C1:C29">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/configs/schemas/main.xlsx
+++ b/configs/schemas/main.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/madeliri/Documents/git/shiny_form/configs/schemas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07037598-774F-A843-9C67-26D8CBECEED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D369536-C475-6640-BC0E-BCF413CBA54B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="30240" windowHeight="19000" xr2:uid="{9A1397C5-2914-6B46-9457-B60C998D9C07}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="80">
   <si>
     <t>part</t>
   </si>
@@ -264,6 +264,18 @@
   </si>
   <si>
     <t>но значение должно быть между 0 и 250</t>
+  </si>
+  <si>
+    <t>inline_table2</t>
+  </si>
+  <si>
+    <t>example_inline_table_2</t>
+  </si>
+  <si>
+    <t>test_inline2.xlsx</t>
+  </si>
+  <si>
+    <t>Пример вложенной таблицы2</t>
   </si>
 </sst>
 </file>
@@ -714,7 +726,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DDED1F0-0BDB-364F-8AF4-EDF00BBB7CEB}">
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" style="7" customWidth="1"/>
@@ -952,111 +964,119 @@
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B16" s="7" t="s">
+      <c r="C16" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F16" s="12"/>
+      <c r="G16" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="H16" s="6"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B17" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C17" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D17" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E17" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F17" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G17" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="5" t="s">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H17" s="6"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C18" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F18" s="12"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="6" t="s">
-        <v>50</v>
-      </c>
+      <c r="H18" s="6"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C19" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F19" s="12"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C20" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D20" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E20" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F19" s="12"/>
-      <c r="G19" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
       <c r="F20" s="12"/>
       <c r="G20" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H20" s="6"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C21" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F21" s="12"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="6" t="s">
-        <v>54</v>
-      </c>
+      <c r="H21" s="6"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C22" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F22" s="12"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C23" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D23" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E23" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="F22" s="12"/>
-      <c r="G22" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
       <c r="F23" s="12"/>
       <c r="G23" s="5" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
@@ -1064,104 +1084,109 @@
       <c r="D24" s="6"/>
       <c r="F24" s="12"/>
       <c r="G24" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H24" s="6"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C25" s="6" t="s">
+      <c r="H25" s="6"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C26" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F25" s="12"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B26" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>67</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E26" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F26" s="12"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B27" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="7" t="s">
         <v>69</v>
-      </c>
-      <c r="F26" s="12"/>
-      <c r="H26" s="6"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C27" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>68</v>
       </c>
       <c r="F27" s="12"/>
       <c r="H27" s="6"/>
-      <c r="I27">
-        <v>1</v>
-      </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C28" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="D28" t="s">
-        <v>8</v>
+        <v>66</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>7</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F28" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="G28" s="11" t="s">
-        <v>19</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="F28" s="12"/>
       <c r="H28" s="6"/>
       <c r="I28">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A29" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>4</v>
+      <c r="C29" s="6" t="s">
+        <v>63</v>
       </c>
       <c r="D29" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F29" s="12"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="1"/>
+        <v>74</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="H29" s="6"/>
       <c r="I29">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A30" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D30" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>18</v>
+      </c>
       <c r="F30" s="12"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="1"/>
+      <c r="I30">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="F31" s="12"/>
@@ -1185,13 +1210,16 @@
       <c r="F37" s="12"/>
     </row>
     <row r="38" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F38" s="6"/>
+      <c r="F38" s="12"/>
     </row>
     <row r="39" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F39" s="6"/>
     </row>
+    <row r="40" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F40" s="6"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C30:D1048576 C1:C29">
+  <conditionalFormatting sqref="C31:D1048576 C1:C30">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/configs/schemas/main.xlsx
+++ b/configs/schemas/main.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/madeliri/Documents/git/shiny_form/configs/schemas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D369536-C475-6640-BC0E-BCF413CBA54B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3769DC71-A754-CF4E-BF6B-07CCC7F89E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="30240" windowHeight="19000" xr2:uid="{9A1397C5-2914-6B46-9457-B60C998D9C07}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="78">
   <si>
     <t>part</t>
   </si>
@@ -80,9 +80,6 @@
     <t>subgroup</t>
   </si>
   <si>
-    <t>inline_table</t>
-  </si>
-  <si>
     <t>radio</t>
   </si>
   <si>
@@ -143,15 +140,9 @@
     <t>example_radio</t>
   </si>
   <si>
-    <t>example_inline_table</t>
-  </si>
-  <si>
     <t>Пример вложенной таблицы</t>
   </si>
   <si>
-    <t>example_inline.xlsx</t>
-  </si>
-  <si>
     <t>example_description</t>
   </si>
   <si>
@@ -269,13 +260,16 @@
     <t>inline_table2</t>
   </si>
   <si>
-    <t>example_inline_table_2</t>
-  </si>
-  <si>
-    <t>test_inline2.xlsx</t>
-  </si>
-  <si>
-    <t>Пример вложенной таблицы2</t>
+    <t>example_inline_table_3</t>
+  </si>
+  <si>
+    <t>Пример вложенной таблицы3</t>
+  </si>
+  <si>
+    <t>Обычный вариант (новый)</t>
+  </si>
+  <si>
+    <t>test_inline3.xlsx</t>
   </si>
 </sst>
 </file>
@@ -726,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DDED1F0-0BDB-364F-8AF4-EDF00BBB7CEB}">
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" style="7" customWidth="1"/>
@@ -756,7 +750,7 @@
         <v>1</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>6</v>
@@ -765,24 +759,24 @@
         <v>11</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>21</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F2" s="12"/>
       <c r="G2" s="5"/>
@@ -790,13 +784,13 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C3" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F3" s="12"/>
       <c r="G3" s="5"/>
@@ -804,13 +798,13 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C4" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F4" s="12"/>
       <c r="G4" s="5"/>
@@ -818,17 +812,17 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C5" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>5</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H5" s="6"/>
     </row>
@@ -837,23 +831,23 @@
       <c r="D6" s="6"/>
       <c r="F6" s="12"/>
       <c r="G6" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H6" s="6"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C7" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F7" s="12"/>
       <c r="G7" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H7" s="6"/>
     </row>
@@ -862,23 +856,23 @@
       <c r="D8" s="6"/>
       <c r="F8" s="12"/>
       <c r="G8" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H8" s="6"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C9" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H9" s="6"/>
     </row>
@@ -887,23 +881,23 @@
       <c r="D10" s="6"/>
       <c r="F10" s="12"/>
       <c r="G10" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H10" s="6"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C11" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>43</v>
-      </c>
       <c r="E11" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F11" s="12"/>
       <c r="G11" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H11" s="6"/>
     </row>
@@ -912,19 +906,19 @@
       <c r="D12" s="6"/>
       <c r="F12" s="12"/>
       <c r="G12" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C13" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="5"/>
@@ -932,13 +926,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C14" s="6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="5"/>
@@ -946,137 +940,131 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B15" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="D15" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H15" s="6"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B16" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F15" s="12"/>
-      <c r="G15" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H15" s="6"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C16" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>76</v>
-      </c>
       <c r="E16" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="F16" s="12"/>
+        <v>43</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>68</v>
+      </c>
       <c r="G16" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="H16" s="6"/>
+        <v>44</v>
+      </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="H17" s="6"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C18" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="G17" s="5" t="s">
+      <c r="E18" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" s="12"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="6" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="H18" s="6"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C19" s="6" t="s">
         <v>49</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F19" s="12"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="6" t="s">
-        <v>50</v>
+      <c r="G19" s="5" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C20" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>55</v>
-      </c>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
       <c r="F20" s="12"/>
       <c r="G20" s="5" t="s">
-        <v>47</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H20" s="6"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
+      <c r="C21" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="F21" s="12"/>
-      <c r="G21" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="H21" s="6"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="6" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C22" s="6" t="s">
         <v>53</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="F22" s="12"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="6" t="s">
-        <v>54</v>
+      <c r="G22" s="5" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C23" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>61</v>
-      </c>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
       <c r="F23" s="12"/>
       <c r="G23" s="5" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
@@ -1084,109 +1072,104 @@
       <c r="D24" s="6"/>
       <c r="F24" s="12"/>
       <c r="G24" s="5" t="s">
-        <v>58</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="H24" s="6"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
+      <c r="C25" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="F25" s="12"/>
-      <c r="G25" s="5" t="s">
+      <c r="G25" s="5"/>
+      <c r="H25" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B26" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="H25" s="6"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C26" s="6" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="F26" s="12"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="6" t="s">
-        <v>60</v>
-      </c>
+      <c r="H26" s="6"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B27" s="7" t="s">
-        <v>62</v>
-      </c>
       <c r="C27" s="6" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F27" s="12"/>
       <c r="H27" s="6"/>
+      <c r="I27">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C28" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>7</v>
+        <v>60</v>
+      </c>
+      <c r="D28" t="s">
+        <v>8</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="F28" s="12"/>
+        <v>71</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="H28" s="6"/>
       <c r="I28">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C29" s="6" t="s">
-        <v>63</v>
+      <c r="A29" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="D29" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F29" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="G29" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="H29" s="6"/>
+        <v>17</v>
+      </c>
+      <c r="F29" s="12"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="1"/>
       <c r="I29">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A30" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D30" t="s">
-        <v>7</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>18</v>
-      </c>
       <c r="F30" s="12"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="1"/>
-      <c r="I30">
-        <v>1</v>
-      </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="F31" s="12"/>
@@ -1210,17 +1193,14 @@
       <c r="F37" s="12"/>
     </row>
     <row r="38" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F38" s="12"/>
+      <c r="F38" s="6"/>
     </row>
     <row r="39" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F39" s="6"/>
     </row>
-    <row r="40" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F40" s="6"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="C31:D1048576 C1:C30">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  <conditionalFormatting sqref="C30:D1048576 C1:C29">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
